--- a/public/DOD-Season-14-Sample-Registrations.xlsx
+++ b/public/DOD-Season-14-Sample-Registrations.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Column guide" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:P14"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="35.83203125" customWidth="1"/>
+    <col min="10" max="10" width="27.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="27.83203125" customWidth="1"/>
+    <col min="14" max="14" width="34.83203125" customWidth="1"/>
+    <col min="15" max="15" width="36.83203125" customWidth="1"/>
+    <col min="16" max="16" width="29.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,6 +452,21 @@
       <c r="K1" t="str">
         <v>Age</v>
       </c>
+      <c r="L1" t="str">
+        <v>Payment screenshot</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Category of Dance 2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Number of People Dancing 2</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Names of all group participants</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Dance Style / Genre 2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -448,100 +482,145 @@
         <v>9876543210</v>
       </c>
       <c r="E2" t="str">
-        <v>Rotary Club Of Madras</v>
+        <v>Rotary Club of Madras North</v>
       </c>
       <c r="F2" t="str">
         <v>Annette</v>
       </c>
       <c r="G2" t="str">
-        <v>Solo - Rs.500</v>
-      </c>
-      <c r="H2" t="str">
+        <v>Solo Dance</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>Freestyle</v>
+        <v>Bharatanatyam</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="L2" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-1/view</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>9/13/2026 22:20:00</v>
+        <v>9/13/2026 22:20:11</v>
       </c>
       <c r="B3" t="str">
-        <v>akshay.lakshmi@example.com</v>
+        <v>diya@example.com</v>
       </c>
       <c r="C3" t="str">
-        <v>Akshay &amp; Lakshmi</v>
+        <v>Diya Patel</v>
       </c>
       <c r="D3" t="str">
-        <v>9876501234</v>
+        <v>9000012345</v>
       </c>
       <c r="E3" t="str">
-        <v>Alandur</v>
+        <v>Rotary Club of Agaram</v>
       </c>
       <c r="F3" t="str">
         <v>Ann</v>
       </c>
       <c r="G3" t="str">
-        <v>Couple - Rs.1,000</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2</v>
+        <v>Solo Dance</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>Lakshmi</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>Western</v>
+        <v>Freestyle Dance</v>
       </c>
       <c r="K3">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="L3" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-2/view</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9/13/2026 22:25:00</v>
+        <v>9/13/2026 22:35:04</v>
       </c>
       <c r="B4" t="str">
-        <v>streetcrew@example.com</v>
+        <v>mallika.demo@example.com</v>
       </c>
       <c r="C4" t="str">
-        <v>Street Crew</v>
+        <v>Mallika S</v>
       </c>
       <c r="D4" t="str">
-        <v>9876511111</v>
+        <v>8248700001</v>
       </c>
       <c r="E4" t="str">
         <v>RC Aarch City Madras</v>
       </c>
       <c r="F4" t="str">
-        <v>Rotaractor</v>
+        <v>Annette</v>
       </c>
       <c r="G4" t="str">
-        <v>Group - Rs.2,000</v>
-      </c>
-      <c r="H4" t="str">
-        <v>5</v>
+        <v>Solo Dance</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>Arjun, Neel, Dev, Ishaan</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>Hip-Hop</v>
+        <v>Western Dance</v>
       </c>
       <c r="K4">
         <v>19</v>
       </c>
+      <c r="L4" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-3/view</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>9/14/2026 10:05:12</v>
+        <v>9/14/2026 09:10:22</v>
       </c>
       <c r="B5" t="str">
         <v>sushmita@example.com</v>
@@ -559,94 +638,648 @@
         <v>Rotarian</v>
       </c>
       <c r="G5" t="str">
-        <v>Solo - Rs.500</v>
-      </c>
-      <c r="H5" t="str">
+        <v>Solo Dance</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>Bharatanatyam</v>
+        <v>Classical Dance</v>
       </c>
       <c r="K5">
         <v>35</v>
       </c>
+      <c r="L5" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-4/view</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>9/14/2026 11:40:00</v>
+        <v>9/14/2026 10:05:40</v>
       </c>
       <c r="B6" t="str">
-        <v>dpl.team@example.com</v>
+        <v>niranchana@example.com</v>
       </c>
       <c r="C6" t="str">
-        <v>North Stars</v>
+        <v>V Niranchana</v>
       </c>
       <c r="D6" t="str">
-        <v>9884011122</v>
+        <v>9600064700</v>
       </c>
       <c r="E6" t="str">
-        <v>Rotary Club of Madras North</v>
+        <v>RC Royapettah</v>
       </c>
       <c r="F6" t="str">
-        <v>DPL (Inter-Club Group)</v>
+        <v>Ann</v>
       </c>
       <c r="G6" t="str">
-        <v>Group - Rs.2,000</v>
-      </c>
-      <c r="H6" t="str">
-        <v>8</v>
+        <v>Solo Dance</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>Riya, Aman, Tara, Kunal, Zoya, Nisha, Yash, Ira</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v>Folk Dance</v>
       </c>
       <c r="K6">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="L6" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-5/view</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>9/15/2026 09:15:44</v>
+        <v>9/14/2026 11:18:02</v>
       </c>
       <c r="B7" t="str">
-        <v>diya.kid@example.com</v>
+        <v>karan.meera@example.com</v>
       </c>
       <c r="C7" t="str">
-        <v>Diya Patel</v>
+        <v>Karan &amp; Meera</v>
       </c>
       <c r="D7" t="str">
-        <v>9000012345</v>
+        <v>9876501234</v>
       </c>
       <c r="E7" t="str">
-        <v>Rotary Club Of Madras</v>
+        <v>Rotary Club of Alandur</v>
       </c>
       <c r="F7" t="str">
         <v>Annette</v>
       </c>
       <c r="G7" t="str">
-        <v>Solo - Rs.500</v>
-      </c>
-      <c r="H7" t="str">
-        <v>1</v>
+        <v>Couple Dance</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
       </c>
       <c r="I7" t="str">
-        <v>N/A</v>
+        <v>Meera</v>
       </c>
       <c r="J7" t="str">
+        <v>Folk Dance</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-6/view</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Couple Dance</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Meera</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Folk Dance</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>9/14/2026 12:40:15</v>
+      </c>
+      <c r="B8" t="str">
+        <v>akshay.lakshmi@example.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Akshay &amp; Lakshmi</v>
+      </c>
+      <c r="D8" t="str">
+        <v>9900433300</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Rotary Club of Madras Connemara</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Rotarian</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Couple Dance</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Lakshmipriya</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Western Dance</v>
+      </c>
+      <c r="K8">
+        <v>44</v>
+      </c>
+      <c r="L8" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-7/view</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Couple Dance</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Lakshmipriya</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Western Dance</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9/14/2026 14:22:08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>shruti@example.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Shruti &amp; Arjun</v>
+      </c>
+      <c r="D9" t="str">
+        <v>9840047595</v>
+      </c>
+      <c r="E9" t="str">
+        <v>RCC Radiance</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Ann</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Couple Dance</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Freestyle Dance</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-8/view</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Couple Dance</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Arjun</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Freestyle Dance</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9/15/2026 09:15:44</v>
+      </c>
+      <c r="B10" t="str">
+        <v>streetcrew@example.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Street Crew</v>
+      </c>
+      <c r="D10" t="str">
+        <v>9876511111</v>
+      </c>
+      <c r="E10" t="str">
+        <v>RC Aarch City Madras</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Rotaractor</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Arjun, Neel, Dev, Ishaan, Kabir</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Hip-Hop Dance</v>
+      </c>
+      <c r="K10">
+        <v>19</v>
+      </c>
+      <c r="L10" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-9/view</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Arjun, Neel, Dev, Ishaan, Kabir</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Hip-Hop Dance</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9/15/2026 10:02:18</v>
+      </c>
+      <c r="B11" t="str">
+        <v>northstars@example.com</v>
+      </c>
+      <c r="C11" t="str">
+        <v>North Stars</v>
+      </c>
+      <c r="D11" t="str">
+        <v>9884011122</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Rotary Club of Madras North</v>
+      </c>
+      <c r="F11" t="str">
+        <v>DPL (Inter-Club Group)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Riya, Aman, Tara, Kunal, Zoya, Nisha, Yash, Ira</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Folk Dance</v>
+      </c>
+      <c r="K11">
+        <v>22</v>
+      </c>
+      <c r="L11" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-10/view</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="N11">
+        <v>8</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Riya, Aman, Tara, Kunal, Zoya, Nisha, Yash, Ira</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Folk Dance</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>9/15/2026 11:30:00</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ann.ensemble@example.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Ann Ensemble</v>
+      </c>
+      <c r="D12" t="str">
+        <v>9003122164</v>
+      </c>
+      <c r="E12" t="str">
+        <v>RC Aarch City Madras</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Ann</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Reshma, Revathy, Shyama, Sindhu, Saranya, Annam, Priya, Seetha lakshmi</v>
+      </c>
+      <c r="J12" t="str">
         <v>Classical Dance</v>
       </c>
-      <c r="K7">
-        <v>11</v>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-11/view</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="N12">
+        <v>8</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Reshma, Revathy, Shyama, Sindhu, Saranya, Annam, Priya, Seetha lakshmi</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Classical Dance</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9/15/2026 12:10:33</v>
+      </c>
+      <c r="B13" t="str">
+        <v>annette.crew@example.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Annette Crew</v>
+      </c>
+      <c r="D13" t="str">
+        <v>8939904999</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Rotary Chennai Neidhal</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Annette</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="H13">
+        <v>7</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Shyamili, Shamini, Gokulraj, Kavinaya, Kanishk, Sarah, Hasini</v>
+      </c>
+      <c r="J13" t="str">
+        <v>K-Pop Dance</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-12/view</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="N13">
+        <v>7</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Shyamili, Shamini, Gokulraj, Kavinaya, Kanishk, Sarah, Hasini</v>
+      </c>
+      <c r="P13" t="str">
+        <v>K-Pop Dance</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9/15/2026 13:45:09</v>
+      </c>
+      <c r="B14" t="str">
+        <v>mixed.team@example.com</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Maithri Mixed</v>
+      </c>
+      <c r="D14" t="str">
+        <v>9566178166</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Chennai Maithri</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Mixed</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Vidyaa, Anila, Rukmini, Sweta</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Freestyle Dance</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>https://drive.google.com/file/d/sample-pay-13/view</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Group Dance</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Vidyaa, Anila, Rukmini, Sweta</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Freestyle Dance</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="72.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>What to enter</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Used by import</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Google Form timestamp</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Ignored</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Email Address</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Registrant email</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Participant Name</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Solo name, couple names, or group name</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Yes — required</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Contact Number</v>
+      </c>
+      <c r="B5" t="str">
+        <v>10-digit mobile</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Rotary Club Name</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Club name</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Participant Type</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Rotarian / Ann / Annette / Rotaractor / DPL (Inter-Club Group) / Mixed</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Category of Dance</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Solo Dance / Couple Dance / Group Dance</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Yes — required</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Number of People Dancing</v>
+      </c>
+      <c r="B9" t="str">
+        <v>1 solo, 2 couple, 3+ group</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Names of Other Participants</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Partner or group members, comma separated. Blank for solo</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Dance Style / Genre</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Bharatanatyam, Hip-Hop Dance, Folk Dance, etc.</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Age</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Years. Needed for Solo and Couple age bands. Group can be blank</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Yes — recommended</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Payment screenshot</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Drive / file URL</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Stored if present</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>